--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -10270,6 +10270,409 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Trikinos</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10303,7 +10706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -10396,7 +10799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -10416,7 +10819,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9315,12 +9315,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -9359,17 +9359,14 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -9384,7 +9381,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -9392,62 +9389,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9479,12 +9471,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9525,22 +9517,22 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Trikinos</t>
+          <t>Trichinosis</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -9550,7 +9542,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -9565,7 +9557,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -9600,17 +9592,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>PHO IDTO current-year monthly preliminary trichinosis (trichinellosis) notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -9623,7 +9615,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -9631,62 +9623,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9718,12 +9705,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -9748,7 +9735,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -9770,68 +9757,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9858,17 +9864,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9893,7 +9899,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -9907,76 +9913,170 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Trikinos</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10138,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -10183,7 +10283,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -10298,12 +10398,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -10328,12 +10428,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -10350,87 +10450,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10457,217 +10538,526 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>D122</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Trichinellosis</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>旋毛虫病</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="inlineStr">
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Trikinos</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>country:SE:national</t>
         </is>
       </c>
-      <c r="AD59" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE59" t="inlineStr">
+      <c r="AE61" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF59" t="inlineStr">
+      <c r="AF61" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG59" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH59" t="inlineStr">
+      <c r="AH61" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
+      <c r="AI61" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>revised</t>
         </is>
       </c>
-      <c r="AN59" t="b">
+      <c r="AN61" t="b">
         <v>1</v>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP59" t="inlineStr">
+      <c r="AP61" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ59" t="inlineStr">
+      <c r="AQ61" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
-      <c r="AT59" t="n">
+      <c r="AT61" t="n">
         <v>2</v>
       </c>
-      <c r="AU59" t="inlineStr">
+      <c r="AU61" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV59" t="inlineStr">
+      <c r="AV61" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AW61" t="inlineStr">
         <is>
           <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
+      <c r="AY61" t="inlineStr">
         <is>
           <t>official_html_csv</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
         </is>
       </c>
-      <c r="BA59" t="inlineStr">
+      <c r="BA61" t="inlineStr">
         <is>
           <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
-      <c r="BB59" t="inlineStr">
+      <c r="BB61" t="inlineStr">
         <is>
           <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BC61" t="inlineStr">
         <is>
           <t>official_html_csv</t>
         </is>
@@ -10789,7 +11179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -10799,7 +11189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -10819,7 +11209,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -10851,7 +11241,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -1569,6 +1569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1717,6 +1722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1865,6 +1875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2013,6 +2028,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2161,6 +2181,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3102,6 +3127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3250,6 +3280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3398,6 +3433,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3546,6 +3586,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4487,6 +4532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4635,6 +4685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4783,6 +4838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4931,6 +4991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5872,6 +5937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6020,6 +6090,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6168,6 +6243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6316,6 +6396,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7257,6 +7342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7405,6 +7495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7553,6 +7648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7701,6 +7801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7849,6 +7954,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8787,6 +8897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8932,6 +9047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9077,6 +9197,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9222,6 +9347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10160,6 +10290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10305,6 +10440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10450,6 +10590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10595,6 +10740,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10688,12 +10838,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -10732,17 +10882,14 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -10757,7 +10904,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -10765,62 +10912,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10852,12 +10994,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -10898,22 +11040,22 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Trikinos</t>
+          <t>Trichinosis</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -10923,7 +11065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -10938,7 +11080,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -10973,17 +11115,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>PHO IDTO current-year monthly preliminary trichinosis (trichinellosis) notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -10996,68 +11138,869 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ61" t="inlineStr">
+      <c r="AQ62" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
-      <c r="AT61" t="n">
+      <c r="AT62" t="n">
         <v>2</v>
       </c>
-      <c r="AU61" t="inlineStr">
+      <c r="AU62" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV61" t="inlineStr">
+      <c r="AV62" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
         </is>
       </c>
-      <c r="AW61" t="inlineStr">
+      <c r="AW62" t="inlineStr">
         <is>
           <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
+      <c r="AY62" t="inlineStr">
         <is>
           <t>official_html_csv</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
         </is>
       </c>
-      <c r="BA61" t="inlineStr">
+      <c r="BA62" t="inlineStr">
         <is>
           <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
-      <c r="BB61" t="inlineStr">
+      <c r="BB62" t="inlineStr">
         <is>
           <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
-      <c r="BC61" t="inlineStr">
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Trikinos</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Trikinos</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
         <is>
           <t>official_html_csv</t>
         </is>
@@ -11096,7 +12039,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11179,7 +12122,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -11189,7 +12132,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -11209,7 +12152,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -4011,11 +4011,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -4033,12 +4028,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4048,11 +4038,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4176,11 +4161,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -4198,12 +4178,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4213,11 +4188,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4341,11 +4311,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -4363,12 +4328,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4378,11 +4338,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4506,11 +4461,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -4528,12 +4478,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -4543,11 +4488,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4671,11 +4611,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -4693,12 +4628,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -4708,11 +4638,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -8073,11 +7998,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -8095,12 +8015,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -8110,11 +8025,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8238,11 +8148,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -8260,12 +8165,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -8275,11 +8175,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8403,11 +8298,6 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -8425,12 +8315,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -8440,11 +8325,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8568,11 +8448,6 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -8590,12 +8465,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -8605,11 +8475,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -11970,11 +11835,6 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -11992,12 +11852,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -12007,11 +11862,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12135,11 +11985,6 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -12157,12 +12002,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -12172,11 +12012,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12300,11 +12135,6 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -12322,12 +12152,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -12337,11 +12162,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12465,11 +12285,6 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -12487,12 +12302,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -12502,11 +12312,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -15867,11 +15672,6 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -15889,12 +15689,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -15904,11 +15699,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16032,11 +15822,6 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -16054,12 +15839,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -16069,11 +15849,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16197,11 +15972,6 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -16219,12 +15989,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -16234,11 +15999,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16362,11 +16122,6 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -16384,12 +16139,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -16399,11 +16149,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -19764,11 +19509,6 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -19786,12 +19526,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
@@ -19801,11 +19536,6 @@
       </c>
       <c r="AT134" t="n">
         <v>1</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19929,11 +19659,6 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -19951,12 +19676,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -19966,11 +19686,6 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -20094,11 +19809,6 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -20116,12 +19826,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -20131,11 +19836,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -20259,11 +19959,6 @@
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -20281,12 +19976,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -20296,11 +19986,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -20424,11 +20109,6 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -20446,12 +20126,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -20461,11 +20136,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -23823,11 +23493,6 @@
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -23845,12 +23510,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -23860,11 +23520,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -23985,11 +23640,6 @@
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -24007,12 +23657,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -24022,11 +23667,6 @@
       </c>
       <c r="AT163" t="n">
         <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -24147,11 +23787,6 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -24169,12 +23804,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -24184,11 +23814,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -24309,11 +23934,6 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -24331,12 +23951,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -24346,11 +23961,6 @@
       </c>
       <c r="AT165" t="n">
         <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -27708,11 +27318,6 @@
       <c r="R189" t="n">
         <v>0</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -27730,12 +27335,7 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
@@ -27745,11 +27345,6 @@
       </c>
       <c r="AT189" t="n">
         <v>1</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -27870,11 +27465,6 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -27892,12 +27482,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
@@ -27907,11 +27492,6 @@
       </c>
       <c r="AT190" t="n">
         <v>1</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -28032,11 +27612,6 @@
       <c r="R191" t="n">
         <v>0</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -28054,12 +27629,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
@@ -28069,11 +27639,6 @@
       </c>
       <c r="AT191" t="n">
         <v>1</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -28194,11 +27759,6 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>HOLD_US_ee74f57307261fdc506341e24d00</t>
@@ -28216,12 +27776,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
@@ -28231,11 +27786,6 @@
       </c>
       <c r="AT192" t="n">
         <v>1</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
